--- a/降圧薬詳細_Ca-ARNI_薬価付き_日本語表_英語タイトル引用付き.xlsx
+++ b/降圧薬詳細_Ca-ARNI_薬価付き_日本語表_英語タイトル引用付き.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawagoeyasuhito/Desktop/jp_outcomes_regimen_selector/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawagoeyasuhito/Desktop/jp_outcomes_mvp_complete_final_backup_20251228_103719/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD7EB205-3537-B54A-8CD3-0D5721BCE33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695B22EE-CEB9-BC46-B8A3-5213A1ADA3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="19100" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="137">
   <si>
     <t>分類</t>
   </si>
@@ -341,6 +341,101 @@
   </si>
   <si>
     <t>J-STAGE薬価資料</t>
+  </si>
+  <si>
+    <t>サイアザイド系利尿薬</t>
+  </si>
+  <si>
+    <t>フルイトラン（トリクロルメチアジド） 1 mg/日（開始量）</t>
+  </si>
+  <si>
+    <t>朝家庭血圧 −10.0/−5.9 mmHg（95%CI −11.0〜−9.0 / −6.4〜−5.3）</t>
+  </si>
+  <si>
+    <t>Kario K, et al. Home blood pressure-lowering effect of a non-steroidal mineralocorticoid receptor blocker, esaxerenone, versus trichlormethiazide for uncontrolled hypertension: the EXCITE-HT randomized controlled study. Hypertens Res. 2024;47:2435-2446.</t>
+  </si>
+  <si>
+    <t>10.4 円/錠</t>
+  </si>
+  <si>
+    <t>3,796 円/年</t>
+  </si>
+  <si>
+    <t>10.4 × 365 = 3,796 円/年</t>
+  </si>
+  <si>
+    <t>フルイトラン（トリクロルメチアジド） 2 mg/日</t>
+  </si>
+  <si>
+    <t>朝家庭血圧 −15.0/−8.9 mmHg（95%CI −11.0〜−9.0 / −6.4〜−5.4）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>非ステロイド型MRA</t>
+  </si>
+  <si>
+    <t>ミネブロ（エサキセレノン） 1.25 mg/日</t>
+  </si>
+  <si>
+    <t>座位血圧 −10.7/−5.0 mmHg（95%CI −13.2〜−8.2 / −6.4〜−3.6）</t>
+  </si>
+  <si>
+    <t>Ito S, et al. Efficacy and safety of esaxerenone (CS-3150) for the treatment of essential hypertension: a phase 2 randomized, placebo-controlled, double-blind study. J Hum Hypertens. 2019;33:542-551.</t>
+  </si>
+  <si>
+    <t>85.7 円/錠</t>
+  </si>
+  <si>
+    <t>31,281 円/年</t>
+  </si>
+  <si>
+    <t>85.7 × 365 = 31,281 円/年</t>
+  </si>
+  <si>
+    <t>ミネブロ（エサキセレノン） 2.5 mg/日</t>
+  </si>
+  <si>
+    <t>座位血圧 −14.3/−7.6 mmHg（95%CI −16.8〜−11.9 / −9.1〜−6.2）</t>
+  </si>
+  <si>
+    <t>151.1 円/錠</t>
+  </si>
+  <si>
+    <t>55,152 円/年</t>
+  </si>
+  <si>
+    <t>151.1 × 365 = 55,152 円/年</t>
+  </si>
+  <si>
+    <t>ミネブロ（エサキセレノン） 5 mg/日</t>
+  </si>
+  <si>
+    <t>座位血圧 −20.6/−10.4 mmHg（95%CI −23.0〜−18.2 / −11.8〜−9.0）</t>
+  </si>
+  <si>
+    <t>260.5 円/錠</t>
+  </si>
+  <si>
+    <t>95,083 円/年</t>
+  </si>
+  <si>
+    <t>260.5 × 365 = 95,083 円/年</t>
+  </si>
+  <si>
+    <t>高尿酸血症・高血糖症・電解質失調（0.1〜5%未満）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>副作用発現率 9.6%、血中カリウム増加 0.0%、糸球体濾過率減少 3.6%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>副作用発現率 8.3%、血中カリウム増加 3.6%</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>副作用発現率 13.6%、血中カリウム増加 3.4%、糸球体濾過率減少 3.4%</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -406,10 +501,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -715,8 +813,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="30.5" customWidth="1"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
+    <col min="8" max="8" width="28.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
@@ -1296,6 +1404,151 @@
       </c>
       <c r="I20" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="135">
+      <c r="A21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="135">
+      <c r="A22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="105">
+      <c r="A23" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="105">
+      <c r="A24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="105">
+      <c r="A25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
